--- a/Data/Raw/PNR_ENV_2022.xlsx
+++ b/Data/Raw/PNR_ENV_2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/perry_1864_osu_edu/Documents/Documents/Research Projects/Powdermill Nature Reserve/PNR_Arthropods/Data/Raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8BB0403-3BDE-4D89-9713-9A723F576F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{C8BB0403-3BDE-4D89-9713-9A723F576F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35B7F3DD-3D3A-4A19-8EF2-849559E98412}"/>
   <bookViews>
-    <workbookView xWindow="-13485" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{CA8C2220-5D77-4368-A0A9-BCAE7FCA22D1}"/>
+    <workbookView xWindow="15315" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{CA8C2220-5D77-4368-A0A9-BCAE7FCA22D1}"/>
   </bookViews>
   <sheets>
     <sheet name="DENSI" sheetId="1" r:id="rId1"/>
@@ -14777,7 +14777,7 @@
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
